--- a/Web/TestCasesWeb/FicherosSeguimiento_logs.xlsx
+++ b/Web/TestCasesWeb/FicherosSeguimiento_logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA646AE-D57B-41CD-85C1-0766DCD1DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C5F796-3A34-4716-9250-4D66BACB0612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="3435" windowWidth="23265" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Num</t>
   </si>
@@ -58,12 +58,6 @@
     <t>LOG004</t>
   </si>
   <si>
-    <t>The Logs' page home</t>
-  </si>
-  <si>
-    <t>1. The logs' page home is correctly.</t>
-  </si>
-  <si>
     <t>1. The users clicks "Logs"</t>
   </si>
   <si>
@@ -119,6 +113,93 @@
   </si>
   <si>
     <t>No se controla que la fecha "Hasta" sea superior a la fecha "Desde": Logs001.jpg</t>
+  </si>
+  <si>
+    <t>The Logs' page</t>
+  </si>
+  <si>
+    <t>1. The logs' page is correctly.</t>
+  </si>
+  <si>
+    <t>1. The restaurant logs are shown.</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant</t>
+  </si>
+  <si>
+    <t>1. The user selects show filters</t>
+  </si>
+  <si>
+    <t>1. The user selects hide filters</t>
+  </si>
+  <si>
+    <t>1. The user can use the filters of logs</t>
+  </si>
+  <si>
+    <t>1. The user can not use the filters of logs</t>
+  </si>
+  <si>
+    <t>1. The user can update</t>
+  </si>
+  <si>
+    <t>1. The logs are updated</t>
+  </si>
+  <si>
+    <t>1. The user selects an action</t>
+  </si>
+  <si>
+    <t>1. The user selects an entity</t>
+  </si>
+  <si>
+    <t>1. The user selects an origin</t>
+  </si>
+  <si>
+    <t>1 . The logs shown are of the action selected</t>
+  </si>
+  <si>
+    <t>1 . The logs shown are of the entity selected</t>
+  </si>
+  <si>
+    <t>1 . The logs shown are of the origin selected</t>
+  </si>
+  <si>
+    <t>1. The user selects a date in "Desde"</t>
+  </si>
+  <si>
+    <t>1. The logs are shown from the date</t>
+  </si>
+  <si>
+    <t>1. The user selects a date in "To"</t>
+  </si>
+  <si>
+    <t>1. The logs are shown to the date</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Limpiar"</t>
+  </si>
+  <si>
+    <t>1. The filters are cleaned</t>
+  </si>
+  <si>
+    <t>1. The user clickt the see icon</t>
+  </si>
+  <si>
+    <t>1. The information of the log is shown.</t>
+  </si>
+  <si>
+    <t>LOG008</t>
+  </si>
+  <si>
+    <t>LOG009</t>
+  </si>
+  <si>
+    <t>LOG010</t>
+  </si>
+  <si>
+    <t>LOG011</t>
+  </si>
+  <si>
+    <t>LOG012</t>
   </si>
 </sst>
 </file>
@@ -603,20 +684,20 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -627,17 +708,23 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G3" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -645,17 +732,23 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="G4" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -663,13 +756,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="G5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -678,144 +777,190 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="G6" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="G7" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="G8" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="G9" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="G13" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H13" s="4"/>
     </row>

--- a/Web/TestCasesWeb/FicherosSeguimiento_logs.xlsx
+++ b/Web/TestCasesWeb/FicherosSeguimiento_logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C5F796-3A34-4716-9250-4D66BACB0612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E890E329-D877-4EE4-94E7-9505864CBC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="3435" windowWidth="23265" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <si>
     <t>Num</t>
   </si>
@@ -79,36 +79,6 @@
     <t>Log by restaurant</t>
   </si>
   <si>
-    <t>Filter: show</t>
-  </si>
-  <si>
-    <t>Filter: hide</t>
-  </si>
-  <si>
-    <t>Filter: update</t>
-  </si>
-  <si>
-    <t>Filter: select action</t>
-  </si>
-  <si>
-    <t>Filter: Select entity</t>
-  </si>
-  <si>
-    <t>Filter: select origin</t>
-  </si>
-  <si>
-    <t>Filter: Select from</t>
-  </si>
-  <si>
-    <t>Filter: Select to</t>
-  </si>
-  <si>
-    <t>Filter: Clear</t>
-  </si>
-  <si>
-    <t>Filter: See</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -200,13 +170,69 @@
   </si>
   <si>
     <t>LOG012</t>
+  </si>
+  <si>
+    <t>Logs: Filter, show</t>
+  </si>
+  <si>
+    <t>Logs: Filter, hide</t>
+  </si>
+  <si>
+    <t>Logs: Filter, update</t>
+  </si>
+  <si>
+    <t>Logs: Filter, select action</t>
+  </si>
+  <si>
+    <t>Logs: Filter, Select entity</t>
+  </si>
+  <si>
+    <t>Logs: Filter, select origin</t>
+  </si>
+  <si>
+    <t>Logs: Filter, Select from</t>
+  </si>
+  <si>
+    <t>Logs: Filter, Select to</t>
+  </si>
+  <si>
+    <t>Logs: Filter, Clear</t>
+  </si>
+  <si>
+    <t>Logs: Filter, See</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19/05/26: No se puede buscar por "Tab" y que saque los resultados de "Table", LOGS002.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Si son valores fijos podría salir un desplegable como en origen.</t>
+    </r>
+  </si>
+  <si>
+    <t>19/05/26: Ordenar listado de acciones, LOGS003.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +262,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -277,7 +310,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -299,6 +332,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -684,13 +720,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="7" t="s">
@@ -711,16 +747,16 @@
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H3" s="6"/>
     </row>
@@ -732,19 +768,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -756,19 +792,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -780,19 +816,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -804,21 +840,21 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -828,43 +864,43 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -873,23 +909,23 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>30</v>
+      <c r="H10" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -897,23 +933,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>30</v>
+      <c r="H11" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -921,22 +957,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -945,22 +981,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H13" s="4"/>
     </row>
